--- a/BUT1/1 - Doc/SemestreBUT1_Dorian1.xlsx
+++ b/BUT1/1 - Doc/SemestreBUT1_Dorian1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="65">
   <si>
     <t>UE1.1</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>Communication avec le millieu professionnel</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -839,28 +836,28 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,48 +1174,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="54"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="53"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -1238,7 +1235,7 @@
       <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="54"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="9" t="s">
         <v>0</v>
       </c>
@@ -1257,11 +1254,11 @@
       <c r="P3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="54"/>
+      <c r="Q3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1288,21 +1285,21 @@
         <f>(13+16+13.75*3)/5</f>
         <v>14.05</v>
       </c>
-      <c r="J4" s="54"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="53"/>
       <c r="S4" s="31" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="D5" s="20">
         <f t="shared" ref="D5:I5" si="0">(D4*K5)/K5</f>
         <v>16</v>
@@ -1327,7 +1324,7 @@
         <f t="shared" si="0"/>
         <v>14.05</v>
       </c>
-      <c r="J5" s="54"/>
+      <c r="J5" s="53"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1346,7 +1343,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="54"/>
+      <c r="Q5" s="53"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1355,21 +1352,21 @@
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="54"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="53"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1394,7 +1391,7 @@
       <c r="G7" s="27"/>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="12">
         <v>42</v>
       </c>
@@ -1405,7 +1402,7 @@
       <c r="N7" s="13"/>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="54"/>
+      <c r="Q7" s="53"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1432,7 +1429,7 @@
         <f>B8</f>
         <v>17.25</v>
       </c>
-      <c r="J8" s="54"/>
+      <c r="J8" s="53"/>
       <c r="K8" s="15">
         <v>12</v>
       </c>
@@ -1445,7 +1442,7 @@
       <c r="P8" s="16">
         <v>5</v>
       </c>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="53"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1469,7 +1466,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="26"/>
-      <c r="J9" s="54"/>
+      <c r="J9" s="53"/>
       <c r="K9" s="15"/>
       <c r="L9" s="1">
         <v>3</v>
@@ -1480,7 +1477,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="16"/>
-      <c r="Q9" s="54"/>
+      <c r="Q9" s="53"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1504,7 +1501,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="54"/>
+      <c r="J10" s="53"/>
       <c r="K10" s="15"/>
       <c r="L10" s="1">
         <v>3</v>
@@ -1515,7 +1512,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="16"/>
-      <c r="Q10" s="54"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1537,7 +1534,7 @@
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="54"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1546,7 +1543,7 @@
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="54"/>
+      <c r="Q11" s="53"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1571,7 +1568,7 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="54"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>15</v>
@@ -1582,7 +1579,7 @@
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="54"/>
+      <c r="Q12" s="53"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1604,7 +1601,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="54"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1">
         <v>15</v>
@@ -1613,7 +1610,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="54"/>
+      <c r="Q13" s="53"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1638,7 +1635,7 @@
         <f>B14</f>
         <v>7.333333333333333</v>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1649,7 +1646,7 @@
       <c r="P14" s="16">
         <v>11</v>
       </c>
-      <c r="Q14" s="54"/>
+      <c r="Q14" s="53"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1674,7 +1671,7 @@
         <f>B15</f>
         <v>10.5</v>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1685,7 +1682,7 @@
       <c r="P15" s="16">
         <v>11</v>
       </c>
-      <c r="Q15" s="54"/>
+      <c r="Q15" s="53"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1713,7 +1710,7 @@
         <f>B16</f>
         <v>8.640625</v>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="15">
         <v>6</v>
       </c>
@@ -1726,7 +1723,7 @@
       <c r="P16" s="16">
         <v>11</v>
       </c>
-      <c r="Q16" s="54"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1754,7 +1751,7 @@
         <f>B17</f>
         <v>16.125</v>
       </c>
-      <c r="J17" s="54"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="15"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1">
@@ -1767,7 +1764,7 @@
       <c r="P17" s="16">
         <v>11</v>
       </c>
-      <c r="Q17" s="54"/>
+      <c r="Q17" s="53"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1788,7 +1785,7 @@
         <f>B18</f>
         <v>10.75</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1797,12 +1794,12 @@
       <c r="P18" s="16">
         <v>11</v>
       </c>
-      <c r="Q18" s="54"/>
+      <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="20">
         <f>((K16*D16)+(K8*D8)+(D7*K7))/K19</f>
         <v>14.7265625</v>
@@ -1827,7 +1824,7 @@
         <f>((P16*I16)+(P8*I8)+(I18*P18)+(I17*P17)+(I15*P15)+(I14*P14))/P19</f>
         <v>11.218142361111111</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="17">
         <v>60</v>
       </c>
@@ -1846,7 +1843,7 @@
       <c r="P19" s="19">
         <v>60</v>
       </c>
-      <c r="Q19" s="54"/>
+      <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1881,7 +1878,7 @@
         <f t="shared" si="1"/>
         <v>12.350885416666666</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="53"/>
       <c r="K20" s="3">
         <v>100</v>
       </c>
@@ -1900,89 +1897,89 @@
       <c r="P20" s="5">
         <v>100</v>
       </c>
-      <c r="Q20" s="54"/>
+      <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="54"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
     </row>
     <row r="23" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="54"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="52"/>
       <c r="D25" s="3" t="s">
         <v>0</v>
@@ -2002,7 +1999,7 @@
       <c r="I25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="54"/>
+      <c r="J25" s="53"/>
       <c r="K25" s="9" t="s">
         <v>0</v>
       </c>
@@ -2021,11 +2018,11 @@
       <c r="P25" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Q25" s="54"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="53"/>
       <c r="C26" s="8" t="s">
         <v>19</v>
       </c>
@@ -2053,7 +2050,7 @@
         <f>(14+11.5+12*3+12.3*5)/10</f>
         <v>12.3</v>
       </c>
-      <c r="J26" s="54"/>
+      <c r="J26" s="53"/>
       <c r="K26" s="12">
         <v>38</v>
       </c>
@@ -2072,11 +2069,11 @@
       <c r="P26" s="14">
         <v>38</v>
       </c>
-      <c r="Q26" s="54"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="54"/>
-      <c r="B27" s="54"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
@@ -2098,7 +2095,7 @@
       <c r="I27" s="45">
         <v>10.75</v>
       </c>
-      <c r="J27" s="54"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="35">
         <v>2</v>
       </c>
@@ -2117,11 +2114,11 @@
       <c r="P27" s="37">
         <v>2</v>
       </c>
-      <c r="Q27" s="54"/>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="55"/>
-      <c r="B28" s="55"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
       <c r="C28" s="52"/>
       <c r="D28" s="7">
         <f>(D26*K26+D27*K27)/K28</f>
@@ -2147,7 +2144,7 @@
         <f t="shared" si="2"/>
         <v>12.2225</v>
       </c>
-      <c r="J28" s="54"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="17">
         <v>40</v>
       </c>
@@ -2166,7 +2163,7 @@
       <c r="P28" s="19">
         <v>40</v>
       </c>
-      <c r="Q28" s="54"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -2175,21 +2172,21 @@
       <c r="B29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="54"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="53"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -2214,7 +2211,7 @@
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="I30" s="28"/>
-      <c r="J30" s="54"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="12">
         <v>21</v>
       </c>
@@ -2225,7 +2222,7 @@
       <c r="N30" s="13"/>
       <c r="O30" s="13"/>
       <c r="P30" s="14"/>
-      <c r="Q30" s="54"/>
+      <c r="Q30" s="53"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -2253,7 +2250,7 @@
         <f>$B31</f>
         <v>15.166666666666666</v>
       </c>
-      <c r="J31" s="54"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="15">
         <v>21</v>
       </c>
@@ -2266,7 +2263,7 @@
       <c r="P31" s="16">
         <v>4</v>
       </c>
-      <c r="Q31" s="54"/>
+      <c r="Q31" s="53"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2291,7 +2288,7 @@
         <v>15.45</v>
       </c>
       <c r="I32" s="26"/>
-      <c r="J32" s="54"/>
+      <c r="J32" s="53"/>
       <c r="K32" s="15">
         <v>12</v>
       </c>
@@ -2302,7 +2299,7 @@
         <v>6</v>
       </c>
       <c r="P32" s="16"/>
-      <c r="Q32" s="54"/>
+      <c r="Q32" s="53"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2326,7 +2323,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="54"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="15"/>
       <c r="L33" s="1">
         <v>12</v>
@@ -2337,7 +2334,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="16"/>
-      <c r="Q33" s="54"/>
+      <c r="Q33" s="53"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2358,7 +2355,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="54"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="15"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1">
@@ -2367,7 +2364,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="16"/>
-      <c r="Q34" s="54"/>
+      <c r="Q34" s="53"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2388,7 +2385,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="54"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2397,7 +2394,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="54"/>
+      <c r="Q35" s="53"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2422,7 +2419,7 @@
         <v>16.375</v>
       </c>
       <c r="I36" s="26"/>
-      <c r="J36" s="54"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>21</v>
@@ -2433,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="P36" s="16"/>
-      <c r="Q36" s="54"/>
+      <c r="Q36" s="53"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2454,7 +2451,7 @@
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="54"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2463,7 +2460,7 @@
       </c>
       <c r="O37" s="1"/>
       <c r="P37" s="16"/>
-      <c r="Q37" s="54"/>
+      <c r="Q37" s="53"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2484,7 +2481,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="54"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1">
         <v>12</v>
@@ -2493,7 +2490,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="16"/>
-      <c r="Q38" s="54"/>
+      <c r="Q38" s="53"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2518,7 +2515,7 @@
         <v>11</v>
       </c>
       <c r="I39" s="26"/>
-      <c r="J39" s="54"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2529,7 +2526,7 @@
         <v>30</v>
       </c>
       <c r="P39" s="16"/>
-      <c r="Q39" s="54"/>
+      <c r="Q39" s="53"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2550,7 +2547,7 @@
         <f>B40</f>
         <v>7</v>
       </c>
-      <c r="J40" s="54"/>
+      <c r="J40" s="53"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2559,7 +2556,7 @@
       <c r="P40" s="16">
         <v>17</v>
       </c>
-      <c r="Q40" s="54"/>
+      <c r="Q40" s="53"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2590,7 +2587,7 @@
         <f>B41</f>
         <v>8.6538461538461533</v>
       </c>
-      <c r="J41" s="54"/>
+      <c r="J41" s="53"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1">
@@ -2605,7 +2602,7 @@
       <c r="P41" s="16">
         <v>17</v>
       </c>
-      <c r="Q41" s="54"/>
+      <c r="Q41" s="53"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2636,7 +2633,7 @@
         <f>$B42</f>
         <v>9.875</v>
       </c>
-      <c r="J42" s="54"/>
+      <c r="J42" s="53"/>
       <c r="K42" s="41">
         <v>6</v>
       </c>
@@ -2651,7 +2648,7 @@
       <c r="P42" s="43">
         <v>11</v>
       </c>
-      <c r="Q42" s="54"/>
+      <c r="Q42" s="53"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2664,9 +2661,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="38"/>
-      <c r="E43" s="39" t="s">
-        <v>65</v>
-      </c>
+      <c r="E43" s="39"/>
       <c r="F43" s="39"/>
       <c r="G43" s="39"/>
       <c r="H43" s="39"/>
@@ -2674,7 +2669,7 @@
         <f>$B43</f>
         <v>12.9</v>
       </c>
-      <c r="J43" s="54"/>
+      <c r="J43" s="53"/>
       <c r="K43" s="41"/>
       <c r="L43" s="42"/>
       <c r="M43" s="42"/>
@@ -2683,12 +2678,12 @@
       <c r="P43" s="43">
         <v>11</v>
       </c>
-      <c r="Q43" s="54"/>
+      <c r="Q43" s="53"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="59"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="55"/>
       <c r="D44" s="20">
         <f>((K42*D42)+(K31*D31)+(D32*K32)+(D30*K30))/K44</f>
         <v>15.353333333333333</v>
@@ -2713,7 +2708,7 @@
         <f>((P41*I41)+(P31*I31)+(I43*P43)+(I42*P42)+(I40*P40))/P44</f>
         <v>9.6217841880341872</v>
       </c>
-      <c r="J44" s="54"/>
+      <c r="J44" s="53"/>
       <c r="K44" s="17">
         <v>60</v>
       </c>
@@ -2732,7 +2727,7 @@
       <c r="P44" s="19">
         <v>60</v>
       </c>
-      <c r="Q44" s="54"/>
+      <c r="Q44" s="53"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -2767,7 +2762,7 @@
         <f t="shared" si="4"/>
         <v>10.662070512820513</v>
       </c>
-      <c r="J45" s="54"/>
+      <c r="J45" s="53"/>
       <c r="K45" s="3">
         <v>100</v>
       </c>
@@ -2786,128 +2781,128 @@
       <c r="P45" s="5">
         <v>100</v>
       </c>
-      <c r="Q45" s="54"/>
+      <c r="Q45" s="53"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="54"/>
-      <c r="J46" s="54"/>
-      <c r="K46" s="54"/>
-      <c r="L46" s="54"/>
-      <c r="M46" s="54"/>
-      <c r="N46" s="54"/>
-      <c r="O46" s="54"/>
-      <c r="P46" s="54"/>
-      <c r="Q46" s="54"/>
+      <c r="A46" s="53"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="53"/>
+      <c r="N46" s="53"/>
+      <c r="O46" s="53"/>
+      <c r="P46" s="53"/>
+      <c r="Q46" s="53"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="54"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="54"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="53"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="53"/>
     </row>
     <row r="50" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="53" t="s">
+      <c r="A50" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="54"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="60"/>
+      <c r="J50" s="60"/>
+      <c r="K50" s="60"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="60"/>
+      <c r="N50" s="60"/>
+      <c r="O50" s="60"/>
+      <c r="P50" s="60"/>
+      <c r="Q50" s="53"/>
     </row>
     <row r="51" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="60"/>
-      <c r="B51" s="60"/>
-      <c r="C51" s="60"/>
-      <c r="D51" s="60"/>
-      <c r="E51" s="60"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="60"/>
-      <c r="J51" s="60"/>
-      <c r="K51" s="60"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="60"/>
-      <c r="N51" s="60"/>
-      <c r="O51" s="60"/>
-      <c r="P51" s="60"/>
-      <c r="Q51" s="54"/>
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="56"/>
+      <c r="P51" s="56"/>
+      <c r="Q51" s="53"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="54"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
+      <c r="A52" s="53"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
       <c r="D52" s="3" t="s">
         <v>0</v>
       </c>
@@ -2926,19 +2921,19 @@
       <c r="I52" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="54"/>
-      <c r="K52" s="54"/>
-      <c r="L52" s="54"/>
-      <c r="M52" s="54"/>
-      <c r="N52" s="54"/>
-      <c r="O52" s="54"/>
-      <c r="P52" s="54"/>
-      <c r="Q52" s="54"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="53"/>
+      <c r="P52" s="53"/>
+      <c r="Q52" s="53"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="50">
         <f>(D45+D20)/2</f>
         <v>15.06271875</v>
@@ -2963,55 +2958,61 @@
         <f t="shared" si="5"/>
         <v>11.506477964743588</v>
       </c>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="53"/>
+      <c r="P53" s="53"/>
+      <c r="Q53" s="53"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="54"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="54"/>
-      <c r="I54" s="54"/>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="54"/>
-      <c r="M54" s="54"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="53"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="53"/>
+      <c r="P54" s="53"/>
+      <c r="Q54" s="53"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A23:P23"/>
+    <mergeCell ref="A50:P50"/>
+    <mergeCell ref="J3:J20"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q55"/>
     <mergeCell ref="A46:P49"/>
     <mergeCell ref="A44:C44"/>
@@ -3028,12 +3029,6 @@
     <mergeCell ref="J25:J45"/>
     <mergeCell ref="K29:P29"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A23:P23"/>
-    <mergeCell ref="A50:P50"/>
-    <mergeCell ref="J3:J20"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D20:I20">
     <cfRule type="colorScale" priority="10">
